--- a/outputs/monitor_xlsx/20260415.xlsx
+++ b/outputs/monitor_xlsx/20260415.xlsx
@@ -544,10 +544,6 @@
           <t>+1.17%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.07%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.73%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.56%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+0.39%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.38%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-1.03%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-0.66%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>553.5億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>337.33億</t>
@@ -811,7 +774,6 @@
           <t>-88.94億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-23.57億</t>
@@ -822,8 +784,6 @@
           <t>-117.86億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>149.68%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>141.26%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>414.25億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>13060口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10645口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-16.12億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-45.46億</t>
@@ -1019,10 +965,6 @@
           <t>-883.85億</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1179,6 +1121,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1299,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,20 +1250,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>84.15000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1.26</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>127729</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>25093</v>
       </c>
       <c r="H4" t="n">
-        <v>200341</v>
+        <v>225434</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1132</v>
@@ -1332,11 +1278,14 @@
         <v>9316</v>
       </c>
       <c r="M4" t="n">
-        <v>38267</v>
+        <v>47583</v>
       </c>
       <c r="N4" t="n">
         <v>-4597561</v>
       </c>
+      <c r="O4" t="n">
+        <v>9.289999999999999</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1359,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>877</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5.66</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>5262</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-656</v>
       </c>
       <c r="H5" t="n">
-        <v>-885</v>
+        <v>-1540</v>
       </c>
       <c r="I5" t="n">
         <v>-18</v>
       </c>
       <c r="J5" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
         <v>110</v>
@@ -1387,11 +1336,14 @@
         <v>2744</v>
       </c>
       <c r="M5" t="n">
-        <v>10776</v>
+        <v>13520</v>
       </c>
       <c r="N5" t="n">
         <v>-78964</v>
       </c>
+      <c r="O5" t="n">
+        <v>2.38</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1414,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1785</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>12877</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1623</v>
       </c>
       <c r="H6" t="n">
-        <v>-791</v>
+        <v>833</v>
       </c>
       <c r="I6" t="n">
         <v>-64</v>
       </c>
       <c r="J6" t="n">
-        <v>-542</v>
+        <v>-606</v>
       </c>
       <c r="K6" t="n">
         <v>157</v>
@@ -1442,11 +1394,14 @@
         <v>4930</v>
       </c>
       <c r="M6" t="n">
-        <v>19638</v>
+        <v>24568</v>
       </c>
       <c r="N6" t="n">
         <v>-649286</v>
       </c>
+      <c r="O6" t="n">
+        <v>15.76</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1469,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>2080</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.22</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>46824</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>4826</v>
       </c>
       <c r="H7" t="n">
-        <v>26561</v>
+        <v>31387</v>
       </c>
       <c r="I7" t="n">
         <v>-138</v>
       </c>
       <c r="J7" t="n">
-        <v>-4487</v>
+        <v>-4626</v>
       </c>
       <c r="K7" t="n">
         <v>1152</v>
@@ -1497,11 +1452,14 @@
         <v>26878</v>
       </c>
       <c r="M7" t="n">
-        <v>109293</v>
+        <v>136171</v>
       </c>
       <c r="N7" t="n">
         <v>-6483035</v>
       </c>
+      <c r="O7" t="n">
+        <v>10.39</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1524,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1970</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>4.23</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>7294</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>575</v>
       </c>
       <c r="H8" t="n">
-        <v>174</v>
+        <v>749</v>
       </c>
       <c r="I8" t="n">
         <v>438</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>994</v>
       </c>
       <c r="K8" t="n">
         <v>326</v>
@@ -1552,11 +1510,14 @@
         <v>1377</v>
       </c>
       <c r="M8" t="n">
-        <v>6560</v>
+        <v>7937</v>
       </c>
       <c r="N8" t="n">
         <v>-140254</v>
       </c>
+      <c r="O8" t="n">
+        <v>18.34</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1579,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>2020</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>2929</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-358</v>
       </c>
       <c r="H9" t="n">
-        <v>-2581</v>
+        <v>-2939</v>
       </c>
       <c r="I9" t="n">
         <v>271</v>
       </c>
       <c r="J9" t="n">
-        <v>1299</v>
+        <v>1571</v>
       </c>
       <c r="K9" t="n">
         <v>92</v>
@@ -1607,11 +1568,14 @@
         <v>1942</v>
       </c>
       <c r="M9" t="n">
-        <v>7563</v>
+        <v>9505</v>
       </c>
       <c r="N9" t="n">
         <v>-106285</v>
       </c>
+      <c r="O9" t="n">
+        <v>22.46</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1634,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>3810</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>5.69</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3998</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>97</v>
       </c>
       <c r="H10" t="n">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="I10" t="n">
         <v>-56</v>
       </c>
       <c r="J10" t="n">
-        <v>-29</v>
+        <v>-85</v>
       </c>
       <c r="K10" t="n">
         <v>198</v>
@@ -1662,11 +1626,14 @@
         <v>1866</v>
       </c>
       <c r="M10" t="n">
-        <v>7464</v>
+        <v>9330</v>
       </c>
       <c r="N10" t="n">
         <v>-89531</v>
       </c>
+      <c r="O10" t="n">
+        <v>27.54</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1689,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2090</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0.72</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>4826</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-1022</v>
+        <v>-822</v>
       </c>
       <c r="I11" t="n">
         <v>-318</v>
       </c>
       <c r="J11" t="n">
-        <v>-532</v>
+        <v>-850</v>
       </c>
       <c r="K11" t="n">
         <v>86</v>
@@ -1717,11 +1684,14 @@
         <v>4337</v>
       </c>
       <c r="M11" t="n">
-        <v>15866</v>
+        <v>20203</v>
       </c>
       <c r="N11" t="n">
         <v>-19532</v>
       </c>
+      <c r="O11" t="n">
+        <v>2.58</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1744,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>9065</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>7.02</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>343</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>113</v>
       </c>
       <c r="H12" t="n">
-        <v>-65</v>
+        <v>48</v>
       </c>
       <c r="I12" t="n">
         <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="K12" t="n">
         <v>16</v>
@@ -1772,11 +1742,14 @@
         <v>279</v>
       </c>
       <c r="M12" t="n">
-        <v>1217</v>
+        <v>1496</v>
       </c>
       <c r="N12" t="n">
         <v>-9010</v>
       </c>
+      <c r="O12" t="n">
+        <v>16.81</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1799,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4814</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>210</v>
       </c>
       <c r="H13" t="n">
-        <v>-243</v>
+        <v>-33</v>
       </c>
       <c r="I13" t="n">
         <v>-345</v>
       </c>
       <c r="J13" t="n">
-        <v>-500</v>
+        <v>-845</v>
       </c>
       <c r="K13" t="n">
         <v>39</v>
@@ -1827,11 +1800,14 @@
         <v>-73</v>
       </c>
       <c r="M13" t="n">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1854,20 +1830,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>533</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12905</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1843</v>
       </c>
       <c r="H14" t="n">
-        <v>-262</v>
+        <v>1581</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-642</v>
@@ -1879,11 +1858,14 @@
         <v>1238</v>
       </c>
       <c r="M14" t="n">
-        <v>1327</v>
+        <v>2565</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1906,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1135</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9046</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-1624</v>
       </c>
       <c r="H15" t="n">
-        <v>-348</v>
+        <v>-1972</v>
       </c>
       <c r="I15" t="n">
         <v>704</v>
       </c>
       <c r="J15" t="n">
-        <v>-2</v>
+        <v>702</v>
       </c>
       <c r="K15" t="n">
         <v>-16</v>
@@ -1934,11 +1916,14 @@
         <v>1008</v>
       </c>
       <c r="M15" t="n">
-        <v>-97</v>
+        <v>911</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1961,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1730</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="F16" t="n">
-        <v>604</v>
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-20</v>
       </c>
       <c r="H16" t="n">
-        <v>-56</v>
+        <v>-76</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K16" t="n">
         <v>-9</v>
@@ -1989,11 +1974,14 @@
         <v>12</v>
       </c>
       <c r="M16" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2016,26 +2004,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>701</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>4.32</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="6" t="n">
         <v>711</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>-40</v>
       </c>
       <c r="H17" t="n">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="I17" t="n">
         <v>-2</v>
       </c>
       <c r="J17" t="n">
-        <v>-78</v>
+        <v>-80</v>
       </c>
       <c r="K17" t="n">
         <v>14</v>
@@ -2044,10 +2032,13 @@
         <v>9111</v>
       </c>
       <c r="M17" t="n">
-        <v>38147</v>
+        <v>47258</v>
       </c>
       <c r="N17" t="n">
         <v>-21768</v>
+      </c>
+      <c r="O17" t="n">
+        <v>56.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>

--- a/outputs/monitor_xlsx/20260415.xlsx
+++ b/outputs/monitor_xlsx/20260415.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2046,165 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22780</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>4491</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2882</v>
+      </c>
+      <c r="I18" t="n">
+        <v>264</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-572</v>
+      </c>
+      <c r="K18" t="n">
+        <v>855</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7166</v>
+      </c>
+      <c r="M18" t="n">
+        <v>34011</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400925</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11.39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>618</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>3579</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-22623</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1386</v>
+      </c>
+      <c r="J19" t="n">
+        <v>28231</v>
+      </c>
+      <c r="K19" t="n">
+        <v>561</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34958</v>
+      </c>
+      <c r="M19" t="n">
+        <v>175036</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393706</v>
+      </c>
+      <c r="O19" t="n">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>656</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17929</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>265</v>
+      </c>
+      <c r="H20" t="n">
+        <v>512</v>
+      </c>
+      <c r="I20" t="n">
+        <v>88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2217</v>
+      </c>
+      <c r="K20" t="n">
+        <v>431</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9012</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41755</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161029</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.08</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
